--- a/AAII_Financials/Yearly/IBM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IBM_YR_FIN.xlsx
@@ -1008,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>830000</v>
+        <v>884000</v>
       </c>
       <c r="E14" s="3">
         <v>3320000</v>
@@ -1128,7 +1128,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>54967000</v>
+        <v>54913000</v>
       </c>
       <c r="E17" s="3">
         <v>52965000</v>
@@ -1179,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>12568000</v>
+        <v>12622000</v>
       </c>
       <c r="E18" s="3">
         <v>9788000</v>
@@ -1302,7 +1302,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>15999000</v>
+        <v>16053000</v>
       </c>
       <c r="E21" s="3">
         <v>13180000</v>
